--- a/Result/profitability/6276.xlsx
+++ b/Result/profitability/6276.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>-0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.19625</v>
+        <v>-0.5075</v>
       </c>
       <c r="N2" t="n">
-        <v>20.43125</v>
+        <v>18.735</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2325</v>
+        <v>-0.73875</v>
       </c>
       <c r="N3" t="n">
-        <v>17.7975</v>
+        <v>14.8575</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>-0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.34</v>
+        <v>-0.93875</v>
       </c>
       <c r="N4" t="n">
-        <v>15.3</v>
+        <v>12.735</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.645</v>
+        <v>-1.065</v>
       </c>
       <c r="N5" t="n">
-        <v>8.935</v>
+        <v>6.6325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6362500000000001</v>
+        <v>-1.1525</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6075</v>
+        <v>3.24125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.725</v>
+        <v>-1.24</v>
       </c>
       <c r="N7" t="n">
-        <v>4.67375</v>
+        <v>1.607499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>-1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.93875</v>
+        <v>-1.31</v>
       </c>
       <c r="N8" t="n">
-        <v>1.143749999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.995</v>
+        <v>-0.9950000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>-1.265000000000001</v>
@@ -2026,7 +2026,7 @@
         <v>-0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.54625</v>
+        <v>-0.5462500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>8.647500000000001</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6276</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>161</v>
+      </c>
+      <c r="D75" t="n">
+        <v>156</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-70</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-43.39%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-85</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.63125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-18.67</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.8761145002346316</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.588235294117647</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-18.42</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.8746438746438746</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
